--- a/roadmap/PLC_SCADA_IIoT_104_Weeks_3_Days_ESP32.xlsx
+++ b/roadmap/PLC_SCADA_IIoT_104_Weeks_3_Days_ESP32.xlsx
@@ -72,7 +72,7 @@
     <col min="11" max="11" width="64" customWidth="1"/>
     <col min="12" max="12" width="22" customWidth="1"/>
     <col min="13" max="13" width="22" customWidth="1"/>
-    <col min="14" max="14" width="49" customWidth="1"/>
+    <col min="14" max="14" width="48" customWidth="1"/>
     <col min="15" max="15" width="22" customWidth="1"/>
     <col min="16" max="16" width="22" customWidth="1"/>
     <col min="17" max="17" width="22" customWidth="1"/>
@@ -86,7 +86,7 @@
       </c>
       <c r="B1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Ngày dự kiến</t>
+          <t xml:space="preserve">Ngày học thực tế</t>
         </is>
       </c>
       <c r="C1" t="inlineStr" s="1">
@@ -96,7 +96,7 @@
       </c>
       <c r="D1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Thứ</t>
+          <t xml:space="preserve">Buổi trong tuần</t>
         </is>
       </c>
       <c r="E1" t="inlineStr" s="1">
@@ -169,17 +169,12 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-11-02</t>
-        </is>
-      </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -252,17 +247,12 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-11-04</t>
-        </is>
-      </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -335,17 +325,12 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-11-06</t>
-        </is>
-      </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -418,17 +403,12 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-11-09</t>
-        </is>
-      </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -501,17 +481,12 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-11-11</t>
-        </is>
-      </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -584,17 +559,12 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-11-13</t>
-        </is>
-      </c>
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -667,17 +637,12 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-11-16</t>
-        </is>
-      </c>
       <c r="C8">
         <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -750,17 +715,12 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-11-18</t>
-        </is>
-      </c>
       <c r="C9">
         <v>3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -833,17 +793,12 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-11-20</t>
-        </is>
-      </c>
       <c r="C10">
         <v>3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -916,17 +871,12 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-11-23</t>
-        </is>
-      </c>
       <c r="C11">
         <v>4</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -999,17 +949,12 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-11-25</t>
-        </is>
-      </c>
       <c r="C12">
         <v>4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1082,17 +1027,12 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-11-27</t>
-        </is>
-      </c>
       <c r="C13">
         <v>4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1165,17 +1105,12 @@
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-11-30</t>
-        </is>
-      </c>
       <c r="C14">
         <v>5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1248,17 +1183,12 @@
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-12-02</t>
-        </is>
-      </c>
       <c r="C15">
         <v>5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1331,17 +1261,12 @@
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-12-04</t>
-        </is>
-      </c>
       <c r="C16">
         <v>5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1414,17 +1339,12 @@
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-12-07</t>
-        </is>
-      </c>
       <c r="C17">
         <v>6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1497,17 +1417,12 @@
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-12-09</t>
-        </is>
-      </c>
       <c r="C18">
         <v>6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1580,17 +1495,12 @@
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-12-11</t>
-        </is>
-      </c>
       <c r="C19">
         <v>6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1663,17 +1573,12 @@
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-12-14</t>
-        </is>
-      </c>
       <c r="C20">
         <v>7</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1746,17 +1651,12 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-12-16</t>
-        </is>
-      </c>
       <c r="C21">
         <v>7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1829,17 +1729,12 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-12-18</t>
-        </is>
-      </c>
       <c r="C22">
         <v>7</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1912,17 +1807,12 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-12-21</t>
-        </is>
-      </c>
       <c r="C23">
         <v>8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1995,17 +1885,12 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-12-23</t>
-        </is>
-      </c>
       <c r="C24">
         <v>8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2078,17 +1963,12 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-12-25</t>
-        </is>
-      </c>
       <c r="C25">
         <v>8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2161,17 +2041,12 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-12-28</t>
-        </is>
-      </c>
       <c r="C26">
         <v>9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2244,17 +2119,12 @@
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-12-30</t>
-        </is>
-      </c>
       <c r="C27">
         <v>9</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2327,17 +2197,12 @@
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-01-01</t>
-        </is>
-      </c>
       <c r="C28">
         <v>9</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2410,17 +2275,12 @@
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-01-04</t>
-        </is>
-      </c>
       <c r="C29">
         <v>10</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2493,17 +2353,12 @@
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-01-06</t>
-        </is>
-      </c>
       <c r="C30">
         <v>10</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2576,17 +2431,12 @@
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-01-08</t>
-        </is>
-      </c>
       <c r="C31">
         <v>10</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2659,17 +2509,12 @@
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-01-11</t>
-        </is>
-      </c>
       <c r="C32">
         <v>11</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2742,17 +2587,12 @@
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-01-13</t>
-        </is>
-      </c>
       <c r="C33">
         <v>11</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2825,17 +2665,12 @@
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-01-15</t>
-        </is>
-      </c>
       <c r="C34">
         <v>11</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2908,17 +2743,12 @@
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-01-18</t>
-        </is>
-      </c>
       <c r="C35">
         <v>12</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2991,17 +2821,12 @@
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-01-20</t>
-        </is>
-      </c>
       <c r="C36">
         <v>12</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3074,17 +2899,12 @@
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-01-22</t>
-        </is>
-      </c>
       <c r="C37">
         <v>12</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3157,17 +2977,12 @@
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-01-25</t>
-        </is>
-      </c>
       <c r="C38">
         <v>13</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3240,17 +3055,12 @@
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-01-27</t>
-        </is>
-      </c>
       <c r="C39">
         <v>13</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3323,17 +3133,12 @@
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-01-29</t>
-        </is>
-      </c>
       <c r="C40">
         <v>13</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3406,17 +3211,12 @@
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-02-01</t>
-        </is>
-      </c>
       <c r="C41">
         <v>14</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3489,17 +3289,12 @@
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-02-03</t>
-        </is>
-      </c>
       <c r="C42">
         <v>14</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3572,17 +3367,12 @@
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-02-05</t>
-        </is>
-      </c>
       <c r="C43">
         <v>14</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3655,17 +3445,12 @@
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-02-08</t>
-        </is>
-      </c>
       <c r="C44">
         <v>15</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3738,17 +3523,12 @@
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-02-10</t>
-        </is>
-      </c>
       <c r="C45">
         <v>15</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3821,17 +3601,12 @@
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-02-12</t>
-        </is>
-      </c>
       <c r="C46">
         <v>15</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3904,17 +3679,12 @@
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-02-15</t>
-        </is>
-      </c>
       <c r="C47">
         <v>16</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3987,17 +3757,12 @@
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-02-17</t>
-        </is>
-      </c>
       <c r="C48">
         <v>16</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4070,17 +3835,12 @@
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-02-19</t>
-        </is>
-      </c>
       <c r="C49">
         <v>16</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4153,17 +3913,12 @@
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-02-22</t>
-        </is>
-      </c>
       <c r="C50">
         <v>17</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4236,17 +3991,12 @@
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-02-24</t>
-        </is>
-      </c>
       <c r="C51">
         <v>17</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4319,17 +4069,12 @@
       <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-02-26</t>
-        </is>
-      </c>
       <c r="C52">
         <v>17</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4402,17 +4147,12 @@
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-03-01</t>
-        </is>
-      </c>
       <c r="C53">
         <v>18</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4485,17 +4225,12 @@
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-03-03</t>
-        </is>
-      </c>
       <c r="C54">
         <v>18</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4568,17 +4303,12 @@
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-03-05</t>
-        </is>
-      </c>
       <c r="C55">
         <v>18</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4651,17 +4381,12 @@
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-03-08</t>
-        </is>
-      </c>
       <c r="C56">
         <v>19</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4734,17 +4459,12 @@
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-03-10</t>
-        </is>
-      </c>
       <c r="C57">
         <v>19</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4817,17 +4537,12 @@
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-03-12</t>
-        </is>
-      </c>
       <c r="C58">
         <v>19</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4900,17 +4615,12 @@
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-03-15</t>
-        </is>
-      </c>
       <c r="C59">
         <v>20</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4983,17 +4693,12 @@
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-03-17</t>
-        </is>
-      </c>
       <c r="C60">
         <v>20</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5066,17 +4771,12 @@
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-03-19</t>
-        </is>
-      </c>
       <c r="C61">
         <v>20</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5149,17 +4849,12 @@
       <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-03-22</t>
-        </is>
-      </c>
       <c r="C62">
         <v>21</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5232,17 +4927,12 @@
       <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-03-24</t>
-        </is>
-      </c>
       <c r="C63">
         <v>21</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5315,17 +5005,12 @@
       <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-03-26</t>
-        </is>
-      </c>
       <c r="C64">
         <v>21</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5398,17 +5083,12 @@
       <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-03-29</t>
-        </is>
-      </c>
       <c r="C65">
         <v>22</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5481,17 +5161,12 @@
       <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-03-31</t>
-        </is>
-      </c>
       <c r="C66">
         <v>22</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5564,17 +5239,12 @@
       <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-04-02</t>
-        </is>
-      </c>
       <c r="C67">
         <v>22</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5647,17 +5317,12 @@
       <c r="A68">
         <v>67</v>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-04-05</t>
-        </is>
-      </c>
       <c r="C68">
         <v>23</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5730,17 +5395,12 @@
       <c r="A69">
         <v>68</v>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-04-07</t>
-        </is>
-      </c>
       <c r="C69">
         <v>23</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5813,17 +5473,12 @@
       <c r="A70">
         <v>69</v>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-04-09</t>
-        </is>
-      </c>
       <c r="C70">
         <v>23</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5896,17 +5551,12 @@
       <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-04-12</t>
-        </is>
-      </c>
       <c r="C71">
         <v>24</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5979,17 +5629,12 @@
       <c r="A72">
         <v>71</v>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-04-14</t>
-        </is>
-      </c>
       <c r="C72">
         <v>24</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6062,17 +5707,12 @@
       <c r="A73">
         <v>72</v>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-04-16</t>
-        </is>
-      </c>
       <c r="C73">
         <v>24</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6145,17 +5785,12 @@
       <c r="A74">
         <v>73</v>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-04-19</t>
-        </is>
-      </c>
       <c r="C74">
         <v>25</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6228,17 +5863,12 @@
       <c r="A75">
         <v>74</v>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-04-21</t>
-        </is>
-      </c>
       <c r="C75">
         <v>25</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6311,17 +5941,12 @@
       <c r="A76">
         <v>75</v>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-04-23</t>
-        </is>
-      </c>
       <c r="C76">
         <v>25</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6394,17 +6019,12 @@
       <c r="A77">
         <v>76</v>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-04-26</t>
-        </is>
-      </c>
       <c r="C77">
         <v>26</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6477,17 +6097,12 @@
       <c r="A78">
         <v>77</v>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-04-28</t>
-        </is>
-      </c>
       <c r="C78">
         <v>26</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -6560,17 +6175,12 @@
       <c r="A79">
         <v>78</v>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-04-30</t>
-        </is>
-      </c>
       <c r="C79">
         <v>26</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -6643,17 +6253,12 @@
       <c r="A80">
         <v>79</v>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-05-03</t>
-        </is>
-      </c>
       <c r="C80">
         <v>27</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -6726,17 +6331,12 @@
       <c r="A81">
         <v>80</v>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-05-05</t>
-        </is>
-      </c>
       <c r="C81">
         <v>27</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -6809,17 +6409,12 @@
       <c r="A82">
         <v>81</v>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-05-07</t>
-        </is>
-      </c>
       <c r="C82">
         <v>27</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -6892,17 +6487,12 @@
       <c r="A83">
         <v>82</v>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-05-10</t>
-        </is>
-      </c>
       <c r="C83">
         <v>28</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -6975,17 +6565,12 @@
       <c r="A84">
         <v>83</v>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-05-12</t>
-        </is>
-      </c>
       <c r="C84">
         <v>28</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7058,17 +6643,12 @@
       <c r="A85">
         <v>84</v>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-05-14</t>
-        </is>
-      </c>
       <c r="C85">
         <v>28</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7141,17 +6721,12 @@
       <c r="A86">
         <v>85</v>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-05-17</t>
-        </is>
-      </c>
       <c r="C86">
         <v>29</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7224,17 +6799,12 @@
       <c r="A87">
         <v>86</v>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-05-19</t>
-        </is>
-      </c>
       <c r="C87">
         <v>29</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7307,17 +6877,12 @@
       <c r="A88">
         <v>87</v>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-05-21</t>
-        </is>
-      </c>
       <c r="C88">
         <v>29</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7390,17 +6955,12 @@
       <c r="A89">
         <v>88</v>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-05-24</t>
-        </is>
-      </c>
       <c r="C89">
         <v>30</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -7473,17 +7033,12 @@
       <c r="A90">
         <v>89</v>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-05-26</t>
-        </is>
-      </c>
       <c r="C90">
         <v>30</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -7556,17 +7111,12 @@
       <c r="A91">
         <v>90</v>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-05-28</t>
-        </is>
-      </c>
       <c r="C91">
         <v>30</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -7639,17 +7189,12 @@
       <c r="A92">
         <v>91</v>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-05-31</t>
-        </is>
-      </c>
       <c r="C92">
         <v>31</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -7722,17 +7267,12 @@
       <c r="A93">
         <v>92</v>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-06-02</t>
-        </is>
-      </c>
       <c r="C93">
         <v>31</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -7805,17 +7345,12 @@
       <c r="A94">
         <v>93</v>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-06-04</t>
-        </is>
-      </c>
       <c r="C94">
         <v>31</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -7888,17 +7423,12 @@
       <c r="A95">
         <v>94</v>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-06-07</t>
-        </is>
-      </c>
       <c r="C95">
         <v>32</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -7971,17 +7501,12 @@
       <c r="A96">
         <v>95</v>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-06-09</t>
-        </is>
-      </c>
       <c r="C96">
         <v>32</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8054,17 +7579,12 @@
       <c r="A97">
         <v>96</v>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-06-11</t>
-        </is>
-      </c>
       <c r="C97">
         <v>32</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8137,17 +7657,12 @@
       <c r="A98">
         <v>97</v>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-06-14</t>
-        </is>
-      </c>
       <c r="C98">
         <v>33</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8220,17 +7735,12 @@
       <c r="A99">
         <v>98</v>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-06-16</t>
-        </is>
-      </c>
       <c r="C99">
         <v>33</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8303,17 +7813,12 @@
       <c r="A100">
         <v>99</v>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-06-18</t>
-        </is>
-      </c>
       <c r="C100">
         <v>33</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8386,17 +7891,12 @@
       <c r="A101">
         <v>100</v>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-06-21</t>
-        </is>
-      </c>
       <c r="C101">
         <v>34</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -8469,17 +7969,12 @@
       <c r="A102">
         <v>101</v>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-06-23</t>
-        </is>
-      </c>
       <c r="C102">
         <v>34</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -8552,17 +8047,12 @@
       <c r="A103">
         <v>102</v>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-06-25</t>
-        </is>
-      </c>
       <c r="C103">
         <v>34</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -8635,17 +8125,12 @@
       <c r="A104">
         <v>103</v>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-06-28</t>
-        </is>
-      </c>
       <c r="C104">
         <v>35</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -8718,17 +8203,12 @@
       <c r="A105">
         <v>104</v>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-06-30</t>
-        </is>
-      </c>
       <c r="C105">
         <v>35</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -8801,17 +8281,12 @@
       <c r="A106">
         <v>105</v>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-07-02</t>
-        </is>
-      </c>
       <c r="C106">
         <v>35</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -8884,17 +8359,12 @@
       <c r="A107">
         <v>106</v>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-07-05</t>
-        </is>
-      </c>
       <c r="C107">
         <v>36</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -8967,17 +8437,12 @@
       <c r="A108">
         <v>107</v>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-07-07</t>
-        </is>
-      </c>
       <c r="C108">
         <v>36</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9050,17 +8515,12 @@
       <c r="A109">
         <v>108</v>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-07-09</t>
-        </is>
-      </c>
       <c r="C109">
         <v>36</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9133,17 +8593,12 @@
       <c r="A110">
         <v>109</v>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-07-12</t>
-        </is>
-      </c>
       <c r="C110">
         <v>37</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9216,17 +8671,12 @@
       <c r="A111">
         <v>110</v>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-07-14</t>
-        </is>
-      </c>
       <c r="C111">
         <v>37</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9299,17 +8749,12 @@
       <c r="A112">
         <v>111</v>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-07-16</t>
-        </is>
-      </c>
       <c r="C112">
         <v>37</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9382,17 +8827,12 @@
       <c r="A113">
         <v>112</v>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-07-19</t>
-        </is>
-      </c>
       <c r="C113">
         <v>38</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -9465,17 +8905,12 @@
       <c r="A114">
         <v>113</v>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-07-21</t>
-        </is>
-      </c>
       <c r="C114">
         <v>38</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -9548,17 +8983,12 @@
       <c r="A115">
         <v>114</v>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-07-23</t>
-        </is>
-      </c>
       <c r="C115">
         <v>38</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -9631,17 +9061,12 @@
       <c r="A116">
         <v>115</v>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-07-26</t>
-        </is>
-      </c>
       <c r="C116">
         <v>39</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -9714,17 +9139,12 @@
       <c r="A117">
         <v>116</v>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-07-28</t>
-        </is>
-      </c>
       <c r="C117">
         <v>39</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -9797,17 +9217,12 @@
       <c r="A118">
         <v>117</v>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-07-30</t>
-        </is>
-      </c>
       <c r="C118">
         <v>39</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -9880,17 +9295,12 @@
       <c r="A119">
         <v>118</v>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-08-02</t>
-        </is>
-      </c>
       <c r="C119">
         <v>40</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -9963,17 +9373,12 @@
       <c r="A120">
         <v>119</v>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-08-04</t>
-        </is>
-      </c>
       <c r="C120">
         <v>40</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -10046,17 +9451,12 @@
       <c r="A121">
         <v>120</v>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-08-06</t>
-        </is>
-      </c>
       <c r="C121">
         <v>40</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -10129,17 +9529,12 @@
       <c r="A122">
         <v>121</v>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-08-09</t>
-        </is>
-      </c>
       <c r="C122">
         <v>41</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -10212,17 +9607,12 @@
       <c r="A123">
         <v>122</v>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-08-11</t>
-        </is>
-      </c>
       <c r="C123">
         <v>41</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -10295,17 +9685,12 @@
       <c r="A124">
         <v>123</v>
       </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-08-13</t>
-        </is>
-      </c>
       <c r="C124">
         <v>41</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -10378,17 +9763,12 @@
       <c r="A125">
         <v>124</v>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-08-16</t>
-        </is>
-      </c>
       <c r="C125">
         <v>42</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -10461,17 +9841,12 @@
       <c r="A126">
         <v>125</v>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-08-18</t>
-        </is>
-      </c>
       <c r="C126">
         <v>42</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -10544,17 +9919,12 @@
       <c r="A127">
         <v>126</v>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-08-20</t>
-        </is>
-      </c>
       <c r="C127">
         <v>42</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -10627,17 +9997,12 @@
       <c r="A128">
         <v>127</v>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-08-23</t>
-        </is>
-      </c>
       <c r="C128">
         <v>43</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -10710,17 +10075,12 @@
       <c r="A129">
         <v>128</v>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-08-25</t>
-        </is>
-      </c>
       <c r="C129">
         <v>43</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -10793,17 +10153,12 @@
       <c r="A130">
         <v>129</v>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-08-27</t>
-        </is>
-      </c>
       <c r="C130">
         <v>43</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -10876,17 +10231,12 @@
       <c r="A131">
         <v>130</v>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-08-30</t>
-        </is>
-      </c>
       <c r="C131">
         <v>44</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -10959,17 +10309,12 @@
       <c r="A132">
         <v>131</v>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-09-01</t>
-        </is>
-      </c>
       <c r="C132">
         <v>44</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11042,17 +10387,12 @@
       <c r="A133">
         <v>132</v>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-09-03</t>
-        </is>
-      </c>
       <c r="C133">
         <v>44</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11125,17 +10465,12 @@
       <c r="A134">
         <v>133</v>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-09-06</t>
-        </is>
-      </c>
       <c r="C134">
         <v>45</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -11208,17 +10543,12 @@
       <c r="A135">
         <v>134</v>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-09-08</t>
-        </is>
-      </c>
       <c r="C135">
         <v>45</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -11291,17 +10621,12 @@
       <c r="A136">
         <v>135</v>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-09-10</t>
-        </is>
-      </c>
       <c r="C136">
         <v>45</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -11374,17 +10699,12 @@
       <c r="A137">
         <v>136</v>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-09-13</t>
-        </is>
-      </c>
       <c r="C137">
         <v>46</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -11457,17 +10777,12 @@
       <c r="A138">
         <v>137</v>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-09-15</t>
-        </is>
-      </c>
       <c r="C138">
         <v>46</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -11540,17 +10855,12 @@
       <c r="A139">
         <v>138</v>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-09-17</t>
-        </is>
-      </c>
       <c r="C139">
         <v>46</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -11623,17 +10933,12 @@
       <c r="A140">
         <v>139</v>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-09-20</t>
-        </is>
-      </c>
       <c r="C140">
         <v>47</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -11706,17 +11011,12 @@
       <c r="A141">
         <v>140</v>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-09-22</t>
-        </is>
-      </c>
       <c r="C141">
         <v>47</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -11789,17 +11089,12 @@
       <c r="A142">
         <v>141</v>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-09-24</t>
-        </is>
-      </c>
       <c r="C142">
         <v>47</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -11872,17 +11167,12 @@
       <c r="A143">
         <v>142</v>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-09-27</t>
-        </is>
-      </c>
       <c r="C143">
         <v>48</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -11955,17 +11245,12 @@
       <c r="A144">
         <v>143</v>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-09-29</t>
-        </is>
-      </c>
       <c r="C144">
         <v>48</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -12038,17 +11323,12 @@
       <c r="A145">
         <v>144</v>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-10-01</t>
-        </is>
-      </c>
       <c r="C145">
         <v>48</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12121,17 +11401,12 @@
       <c r="A146">
         <v>145</v>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-10-04</t>
-        </is>
-      </c>
       <c r="C146">
         <v>49</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -12204,17 +11479,12 @@
       <c r="A147">
         <v>146</v>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-10-06</t>
-        </is>
-      </c>
       <c r="C147">
         <v>49</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -12287,17 +11557,12 @@
       <c r="A148">
         <v>147</v>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-10-08</t>
-        </is>
-      </c>
       <c r="C148">
         <v>49</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -12370,17 +11635,12 @@
       <c r="A149">
         <v>148</v>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-10-11</t>
-        </is>
-      </c>
       <c r="C149">
         <v>50</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -12453,17 +11713,12 @@
       <c r="A150">
         <v>149</v>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-10-13</t>
-        </is>
-      </c>
       <c r="C150">
         <v>50</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -12536,17 +11791,12 @@
       <c r="A151">
         <v>150</v>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-10-15</t>
-        </is>
-      </c>
       <c r="C151">
         <v>50</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -12619,17 +11869,12 @@
       <c r="A152">
         <v>151</v>
       </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-10-18</t>
-        </is>
-      </c>
       <c r="C152">
         <v>51</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -12702,17 +11947,12 @@
       <c r="A153">
         <v>152</v>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-10-20</t>
-        </is>
-      </c>
       <c r="C153">
         <v>51</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -12785,17 +12025,12 @@
       <c r="A154">
         <v>153</v>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-10-22</t>
-        </is>
-      </c>
       <c r="C154">
         <v>51</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -12868,17 +12103,12 @@
       <c r="A155">
         <v>154</v>
       </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-10-25</t>
-        </is>
-      </c>
       <c r="C155">
         <v>52</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -12951,17 +12181,12 @@
       <c r="A156">
         <v>155</v>
       </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-10-27</t>
-        </is>
-      </c>
       <c r="C156">
         <v>52</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13034,17 +12259,12 @@
       <c r="A157">
         <v>156</v>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-10-29</t>
-        </is>
-      </c>
       <c r="C157">
         <v>52</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -13117,17 +12337,12 @@
       <c r="A158">
         <v>157</v>
       </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-11-01</t>
-        </is>
-      </c>
       <c r="C158">
         <v>53</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -13200,17 +12415,12 @@
       <c r="A159">
         <v>158</v>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-11-03</t>
-        </is>
-      </c>
       <c r="C159">
         <v>53</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -13283,17 +12493,12 @@
       <c r="A160">
         <v>159</v>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-11-05</t>
-        </is>
-      </c>
       <c r="C160">
         <v>53</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -13366,17 +12571,12 @@
       <c r="A161">
         <v>160</v>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-11-08</t>
-        </is>
-      </c>
       <c r="C161">
         <v>54</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -13449,17 +12649,12 @@
       <c r="A162">
         <v>161</v>
       </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-11-10</t>
-        </is>
-      </c>
       <c r="C162">
         <v>54</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -13532,17 +12727,12 @@
       <c r="A163">
         <v>162</v>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-11-12</t>
-        </is>
-      </c>
       <c r="C163">
         <v>54</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -13615,17 +12805,12 @@
       <c r="A164">
         <v>163</v>
       </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-11-15</t>
-        </is>
-      </c>
       <c r="C164">
         <v>55</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -13698,17 +12883,12 @@
       <c r="A165">
         <v>164</v>
       </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-11-17</t>
-        </is>
-      </c>
       <c r="C165">
         <v>55</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -13781,17 +12961,12 @@
       <c r="A166">
         <v>165</v>
       </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-11-19</t>
-        </is>
-      </c>
       <c r="C166">
         <v>55</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -13864,17 +13039,12 @@
       <c r="A167">
         <v>166</v>
       </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-11-22</t>
-        </is>
-      </c>
       <c r="C167">
         <v>56</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -13947,17 +13117,12 @@
       <c r="A168">
         <v>167</v>
       </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-11-24</t>
-        </is>
-      </c>
       <c r="C168">
         <v>56</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14030,17 +13195,12 @@
       <c r="A169">
         <v>168</v>
       </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-11-26</t>
-        </is>
-      </c>
       <c r="C169">
         <v>56</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14113,17 +13273,12 @@
       <c r="A170">
         <v>169</v>
       </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-11-29</t>
-        </is>
-      </c>
       <c r="C170">
         <v>57</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -14196,17 +13351,12 @@
       <c r="A171">
         <v>170</v>
       </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-12-01</t>
-        </is>
-      </c>
       <c r="C171">
         <v>57</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -14279,17 +13429,12 @@
       <c r="A172">
         <v>171</v>
       </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-12-03</t>
-        </is>
-      </c>
       <c r="C172">
         <v>57</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -14362,17 +13507,12 @@
       <c r="A173">
         <v>172</v>
       </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-12-06</t>
-        </is>
-      </c>
       <c r="C173">
         <v>58</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -14445,17 +13585,12 @@
       <c r="A174">
         <v>173</v>
       </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-12-08</t>
-        </is>
-      </c>
       <c r="C174">
         <v>58</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -14528,17 +13663,12 @@
       <c r="A175">
         <v>174</v>
       </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-12-10</t>
-        </is>
-      </c>
       <c r="C175">
         <v>58</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -14611,17 +13741,12 @@
       <c r="A176">
         <v>175</v>
       </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-12-13</t>
-        </is>
-      </c>
       <c r="C176">
         <v>59</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -14694,17 +13819,12 @@
       <c r="A177">
         <v>176</v>
       </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-12-15</t>
-        </is>
-      </c>
       <c r="C177">
         <v>59</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -14777,17 +13897,12 @@
       <c r="A178">
         <v>177</v>
       </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-12-17</t>
-        </is>
-      </c>
       <c r="C178">
         <v>59</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -14860,17 +13975,12 @@
       <c r="A179">
         <v>178</v>
       </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-12-20</t>
-        </is>
-      </c>
       <c r="C179">
         <v>60</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -14943,17 +14053,12 @@
       <c r="A180">
         <v>179</v>
       </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-12-22</t>
-        </is>
-      </c>
       <c r="C180">
         <v>60</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -15026,17 +14131,12 @@
       <c r="A181">
         <v>180</v>
       </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-12-24</t>
-        </is>
-      </c>
       <c r="C181">
         <v>60</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -15109,17 +14209,12 @@
       <c r="A182">
         <v>181</v>
       </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-12-27</t>
-        </is>
-      </c>
       <c r="C182">
         <v>61</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -15192,17 +14287,12 @@
       <c r="A183">
         <v>182</v>
       </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-12-29</t>
-        </is>
-      </c>
       <c r="C183">
         <v>61</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -15275,17 +14365,12 @@
       <c r="A184">
         <v>183</v>
       </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-12-31</t>
-        </is>
-      </c>
       <c r="C184">
         <v>61</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -15358,17 +14443,12 @@
       <c r="A185">
         <v>184</v>
       </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-01-03</t>
-        </is>
-      </c>
       <c r="C185">
         <v>62</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -15441,17 +14521,12 @@
       <c r="A186">
         <v>185</v>
       </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-01-05</t>
-        </is>
-      </c>
       <c r="C186">
         <v>62</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -15524,17 +14599,12 @@
       <c r="A187">
         <v>186</v>
       </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-01-07</t>
-        </is>
-      </c>
       <c r="C187">
         <v>62</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -15607,17 +14677,12 @@
       <c r="A188">
         <v>187</v>
       </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-01-10</t>
-        </is>
-      </c>
       <c r="C188">
         <v>63</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -15690,17 +14755,12 @@
       <c r="A189">
         <v>188</v>
       </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-01-12</t>
-        </is>
-      </c>
       <c r="C189">
         <v>63</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -15773,17 +14833,12 @@
       <c r="A190">
         <v>189</v>
       </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-01-14</t>
-        </is>
-      </c>
       <c r="C190">
         <v>63</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -15856,17 +14911,12 @@
       <c r="A191">
         <v>190</v>
       </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-01-17</t>
-        </is>
-      </c>
       <c r="C191">
         <v>64</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -15939,17 +14989,12 @@
       <c r="A192">
         <v>191</v>
       </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-01-19</t>
-        </is>
-      </c>
       <c r="C192">
         <v>64</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -16022,17 +15067,12 @@
       <c r="A193">
         <v>192</v>
       </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-01-21</t>
-        </is>
-      </c>
       <c r="C193">
         <v>64</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -16105,17 +15145,12 @@
       <c r="A194">
         <v>193</v>
       </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-01-24</t>
-        </is>
-      </c>
       <c r="C194">
         <v>65</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -16188,17 +15223,12 @@
       <c r="A195">
         <v>194</v>
       </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-01-26</t>
-        </is>
-      </c>
       <c r="C195">
         <v>65</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -16271,17 +15301,12 @@
       <c r="A196">
         <v>195</v>
       </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-01-28</t>
-        </is>
-      </c>
       <c r="C196">
         <v>65</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -16354,17 +15379,12 @@
       <c r="A197">
         <v>196</v>
       </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-01-31</t>
-        </is>
-      </c>
       <c r="C197">
         <v>66</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -16437,17 +15457,12 @@
       <c r="A198">
         <v>197</v>
       </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-02-02</t>
-        </is>
-      </c>
       <c r="C198">
         <v>66</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -16520,17 +15535,12 @@
       <c r="A199">
         <v>198</v>
       </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-02-04</t>
-        </is>
-      </c>
       <c r="C199">
         <v>66</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -16603,17 +15613,12 @@
       <c r="A200">
         <v>199</v>
       </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-02-07</t>
-        </is>
-      </c>
       <c r="C200">
         <v>67</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -16686,17 +15691,12 @@
       <c r="A201">
         <v>200</v>
       </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-02-09</t>
-        </is>
-      </c>
       <c r="C201">
         <v>67</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -16769,17 +15769,12 @@
       <c r="A202">
         <v>201</v>
       </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-02-11</t>
-        </is>
-      </c>
       <c r="C202">
         <v>67</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -16852,17 +15847,12 @@
       <c r="A203">
         <v>202</v>
       </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-02-14</t>
-        </is>
-      </c>
       <c r="C203">
         <v>68</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -16935,17 +15925,12 @@
       <c r="A204">
         <v>203</v>
       </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-02-16</t>
-        </is>
-      </c>
       <c r="C204">
         <v>68</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -17018,17 +16003,12 @@
       <c r="A205">
         <v>204</v>
       </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-02-18</t>
-        </is>
-      </c>
       <c r="C205">
         <v>68</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -17101,17 +16081,12 @@
       <c r="A206">
         <v>205</v>
       </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-02-21</t>
-        </is>
-      </c>
       <c r="C206">
         <v>69</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -17184,17 +16159,12 @@
       <c r="A207">
         <v>206</v>
       </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-02-23</t>
-        </is>
-      </c>
       <c r="C207">
         <v>69</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -17267,17 +16237,12 @@
       <c r="A208">
         <v>207</v>
       </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-02-25</t>
-        </is>
-      </c>
       <c r="C208">
         <v>69</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -17350,17 +16315,12 @@
       <c r="A209">
         <v>208</v>
       </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-02-28</t>
-        </is>
-      </c>
       <c r="C209">
         <v>70</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -17433,17 +16393,12 @@
       <c r="A210">
         <v>209</v>
       </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-03-01</t>
-        </is>
-      </c>
       <c r="C210">
         <v>70</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -17516,17 +16471,12 @@
       <c r="A211">
         <v>210</v>
       </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-03-03</t>
-        </is>
-      </c>
       <c r="C211">
         <v>70</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -17599,17 +16549,12 @@
       <c r="A212">
         <v>211</v>
       </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-03-06</t>
-        </is>
-      </c>
       <c r="C212">
         <v>71</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -17682,17 +16627,12 @@
       <c r="A213">
         <v>212</v>
       </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-03-08</t>
-        </is>
-      </c>
       <c r="C213">
         <v>71</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -17765,17 +16705,12 @@
       <c r="A214">
         <v>213</v>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-03-10</t>
-        </is>
-      </c>
       <c r="C214">
         <v>71</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -17848,17 +16783,12 @@
       <c r="A215">
         <v>214</v>
       </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-03-13</t>
-        </is>
-      </c>
       <c r="C215">
         <v>72</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -17931,17 +16861,12 @@
       <c r="A216">
         <v>215</v>
       </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-03-15</t>
-        </is>
-      </c>
       <c r="C216">
         <v>72</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -18014,17 +16939,12 @@
       <c r="A217">
         <v>216</v>
       </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-03-17</t>
-        </is>
-      </c>
       <c r="C217">
         <v>72</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -18097,17 +17017,12 @@
       <c r="A218">
         <v>217</v>
       </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-03-20</t>
-        </is>
-      </c>
       <c r="C218">
         <v>73</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -18180,17 +17095,12 @@
       <c r="A219">
         <v>218</v>
       </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-03-22</t>
-        </is>
-      </c>
       <c r="C219">
         <v>73</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -18263,17 +17173,12 @@
       <c r="A220">
         <v>219</v>
       </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-03-24</t>
-        </is>
-      </c>
       <c r="C220">
         <v>73</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -18346,17 +17251,12 @@
       <c r="A221">
         <v>220</v>
       </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-03-27</t>
-        </is>
-      </c>
       <c r="C221">
         <v>74</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -18429,17 +17329,12 @@
       <c r="A222">
         <v>221</v>
       </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-03-29</t>
-        </is>
-      </c>
       <c r="C222">
         <v>74</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -18512,17 +17407,12 @@
       <c r="A223">
         <v>222</v>
       </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-03-31</t>
-        </is>
-      </c>
       <c r="C223">
         <v>74</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -18595,17 +17485,12 @@
       <c r="A224">
         <v>223</v>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-04-03</t>
-        </is>
-      </c>
       <c r="C224">
         <v>75</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -18678,17 +17563,12 @@
       <c r="A225">
         <v>224</v>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-04-05</t>
-        </is>
-      </c>
       <c r="C225">
         <v>75</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -18761,17 +17641,12 @@
       <c r="A226">
         <v>225</v>
       </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-04-07</t>
-        </is>
-      </c>
       <c r="C226">
         <v>75</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -18844,17 +17719,12 @@
       <c r="A227">
         <v>226</v>
       </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-04-10</t>
-        </is>
-      </c>
       <c r="C227">
         <v>76</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -18927,17 +17797,12 @@
       <c r="A228">
         <v>227</v>
       </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-04-12</t>
-        </is>
-      </c>
       <c r="C228">
         <v>76</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -19010,17 +17875,12 @@
       <c r="A229">
         <v>228</v>
       </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-04-14</t>
-        </is>
-      </c>
       <c r="C229">
         <v>76</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -19093,17 +17953,12 @@
       <c r="A230">
         <v>229</v>
       </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-04-17</t>
-        </is>
-      </c>
       <c r="C230">
         <v>77</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -19176,17 +18031,12 @@
       <c r="A231">
         <v>230</v>
       </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-04-19</t>
-        </is>
-      </c>
       <c r="C231">
         <v>77</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -19259,17 +18109,12 @@
       <c r="A232">
         <v>231</v>
       </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-04-21</t>
-        </is>
-      </c>
       <c r="C232">
         <v>77</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -19342,17 +18187,12 @@
       <c r="A233">
         <v>232</v>
       </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-04-24</t>
-        </is>
-      </c>
       <c r="C233">
         <v>78</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -19425,17 +18265,12 @@
       <c r="A234">
         <v>233</v>
       </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-04-26</t>
-        </is>
-      </c>
       <c r="C234">
         <v>78</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -19508,17 +18343,12 @@
       <c r="A235">
         <v>234</v>
       </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-04-28</t>
-        </is>
-      </c>
       <c r="C235">
         <v>78</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -19591,17 +18421,12 @@
       <c r="A236">
         <v>235</v>
       </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-05-01</t>
-        </is>
-      </c>
       <c r="C236">
         <v>79</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -19674,17 +18499,12 @@
       <c r="A237">
         <v>236</v>
       </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-05-03</t>
-        </is>
-      </c>
       <c r="C237">
         <v>79</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -19757,17 +18577,12 @@
       <c r="A238">
         <v>237</v>
       </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-05-05</t>
-        </is>
-      </c>
       <c r="C238">
         <v>79</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -19840,17 +18655,12 @@
       <c r="A239">
         <v>238</v>
       </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-05-08</t>
-        </is>
-      </c>
       <c r="C239">
         <v>80</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -19923,17 +18733,12 @@
       <c r="A240">
         <v>239</v>
       </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-05-10</t>
-        </is>
-      </c>
       <c r="C240">
         <v>80</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -20006,17 +18811,12 @@
       <c r="A241">
         <v>240</v>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-05-12</t>
-        </is>
-      </c>
       <c r="C241">
         <v>80</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -20089,17 +18889,12 @@
       <c r="A242">
         <v>241</v>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-05-15</t>
-        </is>
-      </c>
       <c r="C242">
         <v>81</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -20172,17 +18967,12 @@
       <c r="A243">
         <v>242</v>
       </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-05-17</t>
-        </is>
-      </c>
       <c r="C243">
         <v>81</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -20255,17 +19045,12 @@
       <c r="A244">
         <v>243</v>
       </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-05-19</t>
-        </is>
-      </c>
       <c r="C244">
         <v>81</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -20338,17 +19123,12 @@
       <c r="A245">
         <v>244</v>
       </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-05-22</t>
-        </is>
-      </c>
       <c r="C245">
         <v>82</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -20421,17 +19201,12 @@
       <c r="A246">
         <v>245</v>
       </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-05-24</t>
-        </is>
-      </c>
       <c r="C246">
         <v>82</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -20504,17 +19279,12 @@
       <c r="A247">
         <v>246</v>
       </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-05-26</t>
-        </is>
-      </c>
       <c r="C247">
         <v>82</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -20587,17 +19357,12 @@
       <c r="A248">
         <v>247</v>
       </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-05-29</t>
-        </is>
-      </c>
       <c r="C248">
         <v>83</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -20670,17 +19435,12 @@
       <c r="A249">
         <v>248</v>
       </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-05-31</t>
-        </is>
-      </c>
       <c r="C249">
         <v>83</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -20753,17 +19513,12 @@
       <c r="A250">
         <v>249</v>
       </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-06-02</t>
-        </is>
-      </c>
       <c r="C250">
         <v>83</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -20836,17 +19591,12 @@
       <c r="A251">
         <v>250</v>
       </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-06-05</t>
-        </is>
-      </c>
       <c r="C251">
         <v>84</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -20919,17 +19669,12 @@
       <c r="A252">
         <v>251</v>
       </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-06-07</t>
-        </is>
-      </c>
       <c r="C252">
         <v>84</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -21002,17 +19747,12 @@
       <c r="A253">
         <v>252</v>
       </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-06-09</t>
-        </is>
-      </c>
       <c r="C253">
         <v>84</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -21085,17 +19825,12 @@
       <c r="A254">
         <v>253</v>
       </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-06-12</t>
-        </is>
-      </c>
       <c r="C254">
         <v>85</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -21168,17 +19903,12 @@
       <c r="A255">
         <v>254</v>
       </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-06-14</t>
-        </is>
-      </c>
       <c r="C255">
         <v>85</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -21251,17 +19981,12 @@
       <c r="A256">
         <v>255</v>
       </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-06-16</t>
-        </is>
-      </c>
       <c r="C256">
         <v>85</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -21334,17 +20059,12 @@
       <c r="A257">
         <v>256</v>
       </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-06-19</t>
-        </is>
-      </c>
       <c r="C257">
         <v>86</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -21417,17 +20137,12 @@
       <c r="A258">
         <v>257</v>
       </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-06-21</t>
-        </is>
-      </c>
       <c r="C258">
         <v>86</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -21500,17 +20215,12 @@
       <c r="A259">
         <v>258</v>
       </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-06-23</t>
-        </is>
-      </c>
       <c r="C259">
         <v>86</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -21583,17 +20293,12 @@
       <c r="A260">
         <v>259</v>
       </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-06-26</t>
-        </is>
-      </c>
       <c r="C260">
         <v>87</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -21666,17 +20371,12 @@
       <c r="A261">
         <v>260</v>
       </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-06-28</t>
-        </is>
-      </c>
       <c r="C261">
         <v>87</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -21749,17 +20449,12 @@
       <c r="A262">
         <v>261</v>
       </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-06-30</t>
-        </is>
-      </c>
       <c r="C262">
         <v>87</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -21832,17 +20527,12 @@
       <c r="A263">
         <v>262</v>
       </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-07-03</t>
-        </is>
-      </c>
       <c r="C263">
         <v>88</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -21915,17 +20605,12 @@
       <c r="A264">
         <v>263</v>
       </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-07-05</t>
-        </is>
-      </c>
       <c r="C264">
         <v>88</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -21998,17 +20683,12 @@
       <c r="A265">
         <v>264</v>
       </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-07-07</t>
-        </is>
-      </c>
       <c r="C265">
         <v>88</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -22081,17 +20761,12 @@
       <c r="A266">
         <v>265</v>
       </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-07-10</t>
-        </is>
-      </c>
       <c r="C266">
         <v>89</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -22164,17 +20839,12 @@
       <c r="A267">
         <v>266</v>
       </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-07-12</t>
-        </is>
-      </c>
       <c r="C267">
         <v>89</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -22247,17 +20917,12 @@
       <c r="A268">
         <v>267</v>
       </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-07-14</t>
-        </is>
-      </c>
       <c r="C268">
         <v>89</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -22330,17 +20995,12 @@
       <c r="A269">
         <v>268</v>
       </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-07-17</t>
-        </is>
-      </c>
       <c r="C269">
         <v>90</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -22413,17 +21073,12 @@
       <c r="A270">
         <v>269</v>
       </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-07-19</t>
-        </is>
-      </c>
       <c r="C270">
         <v>90</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -22496,17 +21151,12 @@
       <c r="A271">
         <v>270</v>
       </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-07-21</t>
-        </is>
-      </c>
       <c r="C271">
         <v>90</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -22579,17 +21229,12 @@
       <c r="A272">
         <v>271</v>
       </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-07-24</t>
-        </is>
-      </c>
       <c r="C272">
         <v>91</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -22662,17 +21307,12 @@
       <c r="A273">
         <v>272</v>
       </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-07-26</t>
-        </is>
-      </c>
       <c r="C273">
         <v>91</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -22745,17 +21385,12 @@
       <c r="A274">
         <v>273</v>
       </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-07-28</t>
-        </is>
-      </c>
       <c r="C274">
         <v>91</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -22828,17 +21463,12 @@
       <c r="A275">
         <v>274</v>
       </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-07-31</t>
-        </is>
-      </c>
       <c r="C275">
         <v>92</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -22911,17 +21541,12 @@
       <c r="A276">
         <v>275</v>
       </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-08-02</t>
-        </is>
-      </c>
       <c r="C276">
         <v>92</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -22994,17 +21619,12 @@
       <c r="A277">
         <v>276</v>
       </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-08-04</t>
-        </is>
-      </c>
       <c r="C277">
         <v>92</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -23077,17 +21697,12 @@
       <c r="A278">
         <v>277</v>
       </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-08-07</t>
-        </is>
-      </c>
       <c r="C278">
         <v>93</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -23160,17 +21775,12 @@
       <c r="A279">
         <v>278</v>
       </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-08-09</t>
-        </is>
-      </c>
       <c r="C279">
         <v>93</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -23243,17 +21853,12 @@
       <c r="A280">
         <v>279</v>
       </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-08-11</t>
-        </is>
-      </c>
       <c r="C280">
         <v>93</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -23326,17 +21931,12 @@
       <c r="A281">
         <v>280</v>
       </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-08-14</t>
-        </is>
-      </c>
       <c r="C281">
         <v>94</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -23409,17 +22009,12 @@
       <c r="A282">
         <v>281</v>
       </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-08-16</t>
-        </is>
-      </c>
       <c r="C282">
         <v>94</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -23492,17 +22087,12 @@
       <c r="A283">
         <v>282</v>
       </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-08-18</t>
-        </is>
-      </c>
       <c r="C283">
         <v>94</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -23575,17 +22165,12 @@
       <c r="A284">
         <v>283</v>
       </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-08-21</t>
-        </is>
-      </c>
       <c r="C284">
         <v>95</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -23658,17 +22243,12 @@
       <c r="A285">
         <v>284</v>
       </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-08-23</t>
-        </is>
-      </c>
       <c r="C285">
         <v>95</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -23741,17 +22321,12 @@
       <c r="A286">
         <v>285</v>
       </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-08-25</t>
-        </is>
-      </c>
       <c r="C286">
         <v>95</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -23824,17 +22399,12 @@
       <c r="A287">
         <v>286</v>
       </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-08-28</t>
-        </is>
-      </c>
       <c r="C287">
         <v>96</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -23907,17 +22477,12 @@
       <c r="A288">
         <v>287</v>
       </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-08-30</t>
-        </is>
-      </c>
       <c r="C288">
         <v>96</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -23990,17 +22555,12 @@
       <c r="A289">
         <v>288</v>
       </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-09-01</t>
-        </is>
-      </c>
       <c r="C289">
         <v>96</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -24073,17 +22633,12 @@
       <c r="A290">
         <v>289</v>
       </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-09-04</t>
-        </is>
-      </c>
       <c r="C290">
         <v>97</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -24156,17 +22711,12 @@
       <c r="A291">
         <v>290</v>
       </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-09-06</t>
-        </is>
-      </c>
       <c r="C291">
         <v>97</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -24239,17 +22789,12 @@
       <c r="A292">
         <v>291</v>
       </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-09-08</t>
-        </is>
-      </c>
       <c r="C292">
         <v>97</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -24322,17 +22867,12 @@
       <c r="A293">
         <v>292</v>
       </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-09-11</t>
-        </is>
-      </c>
       <c r="C293">
         <v>98</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -24405,17 +22945,12 @@
       <c r="A294">
         <v>293</v>
       </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-09-13</t>
-        </is>
-      </c>
       <c r="C294">
         <v>98</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -24488,17 +23023,12 @@
       <c r="A295">
         <v>294</v>
       </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-09-15</t>
-        </is>
-      </c>
       <c r="C295">
         <v>98</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -24571,17 +23101,12 @@
       <c r="A296">
         <v>295</v>
       </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-09-18</t>
-        </is>
-      </c>
       <c r="C296">
         <v>99</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -24654,17 +23179,12 @@
       <c r="A297">
         <v>296</v>
       </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-09-20</t>
-        </is>
-      </c>
       <c r="C297">
         <v>99</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -24737,17 +23257,12 @@
       <c r="A298">
         <v>297</v>
       </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-09-22</t>
-        </is>
-      </c>
       <c r="C298">
         <v>99</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -24820,17 +23335,12 @@
       <c r="A299">
         <v>298</v>
       </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-09-25</t>
-        </is>
-      </c>
       <c r="C299">
         <v>100</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -24903,17 +23413,12 @@
       <c r="A300">
         <v>299</v>
       </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-09-27</t>
-        </is>
-      </c>
       <c r="C300">
         <v>100</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -24986,17 +23491,12 @@
       <c r="A301">
         <v>300</v>
       </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-09-29</t>
-        </is>
-      </c>
       <c r="C301">
         <v>100</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -25069,17 +23569,12 @@
       <c r="A302">
         <v>301</v>
       </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-10-02</t>
-        </is>
-      </c>
       <c r="C302">
         <v>101</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -25152,17 +23647,12 @@
       <c r="A303">
         <v>302</v>
       </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-10-04</t>
-        </is>
-      </c>
       <c r="C303">
         <v>101</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -25235,17 +23725,12 @@
       <c r="A304">
         <v>303</v>
       </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-10-06</t>
-        </is>
-      </c>
       <c r="C304">
         <v>101</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -25318,17 +23803,12 @@
       <c r="A305">
         <v>304</v>
       </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-10-09</t>
-        </is>
-      </c>
       <c r="C305">
         <v>102</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -25401,17 +23881,12 @@
       <c r="A306">
         <v>305</v>
       </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-10-11</t>
-        </is>
-      </c>
       <c r="C306">
         <v>102</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -25484,17 +23959,12 @@
       <c r="A307">
         <v>306</v>
       </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-10-13</t>
-        </is>
-      </c>
       <c r="C307">
         <v>102</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -25567,17 +24037,12 @@
       <c r="A308">
         <v>307</v>
       </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-10-16</t>
-        </is>
-      </c>
       <c r="C308">
         <v>103</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -25650,17 +24115,12 @@
       <c r="A309">
         <v>308</v>
       </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-10-18</t>
-        </is>
-      </c>
       <c r="C309">
         <v>103</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -25733,17 +24193,12 @@
       <c r="A310">
         <v>309</v>
       </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-10-20</t>
-        </is>
-      </c>
       <c r="C310">
         <v>103</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -25816,17 +24271,12 @@
       <c r="A311">
         <v>310</v>
       </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-10-23</t>
-        </is>
-      </c>
       <c r="C311">
         <v>104</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Hai</t>
+          <t xml:space="preserve">Buổi 1/3</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -25899,17 +24349,12 @@
       <c r="A312">
         <v>311</v>
       </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-10-25</t>
-        </is>
-      </c>
       <c r="C312">
         <v>104</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Tư</t>
+          <t xml:space="preserve">Buổi 2/3</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -25982,17 +24427,12 @@
       <c r="A313">
         <v>312</v>
       </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-10-27</t>
-        </is>
-      </c>
       <c r="C313">
         <v>104</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu</t>
+          <t xml:space="preserve">Buổi 3/3</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -31359,48 +29799,48 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Study days</t>
+          <t xml:space="preserve">Lịch linh hoạt</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monday / Wednesday / Friday</t>
+          <t xml:space="preserve">3 buổi bất kỳ mỗi tuần; 120 phút/buổi; không gán thứ cố định</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rest days</t>
+          <t xml:space="preserve">Ngày không học</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuesday / Thursday / Saturday / Sunday</t>
+          <t xml:space="preserve">Tùy chọn; không tự đánh dấu bỏ lỡ hay hoàn thành</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start</t>
+          <t xml:space="preserve">Ngày bắt đầu</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-02</t>
+          <t xml:space="preserve">Không ấn định; ghi ngày thực tế khi học</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">End</t>
+          <t xml:space="preserve">Ngày kết thúc</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-27</t>
+          <t xml:space="preserve">Không ấn định; phụ thuộc tiến độ thực tế</t>
         </is>
       </c>
     </row>
